--- a/Taller_Dualidad_Solver_Completo1.xlsx
+++ b/Taller_Dualidad_Solver_Completo1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp-2522-la\Documents\GitHub\ExcelSolverPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66bf0d0917e3adb/Documentos/GitHub/ExcelSolverPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA39E689-899D-490F-8B8B-B9FE1E44DD6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="971" documentId="8_{BA39E689-899D-490F-8B8B-B9FE1E44DD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8B954D-59FA-46B5-B5FD-81A0D7AF5D32}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="11625" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E1 - Primal" sheetId="1" r:id="rId1"/>
@@ -25,43 +25,51 @@
     <sheet name="E3 - Dual" sheetId="6" r:id="rId10"/>
     <sheet name="E4 - Primal" sheetId="7" r:id="rId11"/>
     <sheet name="Informe de respuestas 1" sheetId="17" r:id="rId12"/>
-    <sheet name="E4 - Dual" sheetId="8" r:id="rId13"/>
+    <sheet name="Answer Report 1" sheetId="22" r:id="rId13"/>
+    <sheet name="E4 - Dual" sheetId="8" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="2" hidden="1">'E1 - Dual'!$B$2:$D$2</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'E1 - Primal'!$B$2:$D$2</definedName>
     <definedName name="solver_adj" localSheetId="6" hidden="1">'E2 - Dual'!$B$2:$G$2</definedName>
     <definedName name="solver_adj" localSheetId="4" hidden="1">'E2 - Primal'!$B$2:$E$2</definedName>
+    <definedName name="solver_adj" localSheetId="13" hidden="1">'E4 - Dual'!$B$2:$E$2</definedName>
     <definedName name="solver_adj" localSheetId="10" hidden="1">'E4 - Primal'!$B$2:$D$2</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="13" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="10" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">'E1 - Dual'!$E$4</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'E1 - Primal'!$E$4</definedName>
     <definedName name="solver_lhs1" localSheetId="6" hidden="1">'E2 - Dual'!$H$4:$H$7</definedName>
     <definedName name="solver_lhs1" localSheetId="4" hidden="1">'E2 - Primal'!$F$4:$F$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="13" hidden="1">'E4 - Dual'!$F$4:$F$6</definedName>
     <definedName name="solver_lhs1" localSheetId="10" hidden="1">'E4 - Primal'!$E$4</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'E1 - Dual'!$E$5</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'E1 - Primal'!$E$5</definedName>
@@ -75,61 +83,73 @@
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="13" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="10" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="13" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="10" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="10" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">'E1 - Dual'!$B$8</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'E1 - Primal'!$B$8</definedName>
     <definedName name="solver_opt" localSheetId="6" hidden="1">'E2 - Dual'!$B$9</definedName>
     <definedName name="solver_opt" localSheetId="4" hidden="1">'E2 - Primal'!$B$8</definedName>
+    <definedName name="solver_opt" localSheetId="13" hidden="1">'E4 - Dual'!$B$8</definedName>
     <definedName name="solver_opt" localSheetId="10" hidden="1">'E4 - Primal'!$B$8</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="13" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="10" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="10" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
@@ -143,6 +163,7 @@
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'E1 - Primal'!$G$4</definedName>
     <definedName name="solver_rhs1" localSheetId="6" hidden="1">'E2 - Dual'!$J$4:$J$7</definedName>
     <definedName name="solver_rhs1" localSheetId="4" hidden="1">'E2 - Primal'!$H$4:$H$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="13" hidden="1">'E4 - Dual'!$H$4:$H$6</definedName>
     <definedName name="solver_rhs1" localSheetId="10" hidden="1">'E4 - Primal'!$G$4</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">'E1 - Dual'!$G$5</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'E1 - Primal'!$G$5</definedName>
@@ -156,59 +177,82 @@
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="13" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="10" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="13" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="10" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="4" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="13" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="10" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="13" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="13" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="160">
   <si>
     <t>Variables</t>
   </si>
@@ -652,6 +696,42 @@
   </si>
   <si>
     <t>$E$6=$G$6</t>
+  </si>
+  <si>
+    <t>y4</t>
+  </si>
+  <si>
+    <t>Variables a encontrar y4</t>
+  </si>
+  <si>
+    <t>$F$4&lt;=$H$4</t>
+  </si>
+  <si>
+    <t>$F$5&lt;=$H$5</t>
+  </si>
+  <si>
+    <t>$F$6&lt;=$H$6</t>
+  </si>
+  <si>
+    <t>Hoja de cálculo: [Taller_Dualidad_Solver_Completo1.xlsx]E4 - Dual</t>
+  </si>
+  <si>
+    <t>Informe creado: 2026-10-22 5:56:52 PM</t>
+  </si>
+  <si>
+    <t>Resultado: Solver encontró una solución.  Se cumplen todas las restricciones y condiciones óptimas.</t>
+  </si>
+  <si>
+    <t>Tiempo de la solución: 0.078 segundos.</t>
+  </si>
+  <si>
+    <t>Iteraciones:: 2 Subproblemas: 0</t>
+  </si>
+  <si>
+    <t>Tiempo máximo Ilimitado,  Iteraciones: Unlimited, Precisión 0.000001, Usar escala automática</t>
+  </si>
+  <si>
+    <t>Máximo de subproblemas Ilimitado, Máximo de soluciones de enteros Ilimitado, Tolerancia de enteros 1%, Asumir no negativo.</t>
   </si>
 </sst>
 </file>
@@ -661,7 +741,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -720,6 +800,20 @@
       <b/>
       <sz val="10"/>
       <color indexed="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -803,7 +897,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -824,6 +918,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -831,17 +931,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1243,6 +1333,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -1441,11 +1535,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
     <col min="2" max="4" width="3" customWidth="1"/>
@@ -1455,7 +1549,7 @@
     <col min="8" max="8" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1473,7 +1567,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1491,7 +1585,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1511,7 +1605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1539,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1567,7 +1661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1595,7 +1689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1613,7 +1707,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1643,11 +1737,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja10">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="5" width="3" customWidth="1"/>
@@ -1657,7 +1751,7 @@
     <col min="9" max="9" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1678,7 +1772,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1691,7 +1785,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1712,7 +1806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1731,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1750,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1769,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1782,7 +1876,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1805,11 +1899,11 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja11">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" customWidth="1"/>
@@ -1820,7 +1914,7 @@
     <col min="8" max="8" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1838,7 +1932,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1856,7 +1950,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1876,7 +1970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1904,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1928,11 +2022,11 @@
         <v>20</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" ref="H4:H6" si="1">G5-E5</f>
+        <f t="shared" ref="H5:H6" si="1">G5-E5</f>
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1960,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1978,7 +2072,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -2001,8 +2095,9 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C1062C-39FD-49D7-AF33-C56F9F03DC1B}">
+  <sheetPr codeName="Hoja12"/>
   <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -2012,269 +2107,263 @@
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:5" collapsed="1">
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:5" collapsed="1"/>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1">
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1">
-      <c r="B15" s="19" t="s">
+    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1">
-      <c r="B16" s="14" t="s">
+    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="17">
-        <v>0</v>
-      </c>
-      <c r="E16" s="17">
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
         <v>-31.25</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.5" thickBot="1">
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.5" thickBot="1">
-      <c r="B20" s="19" t="s">
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="B21" s="23" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-    </row>
-    <row r="22" spans="1:7" hidden="1" outlineLevel="1">
-      <c r="B22" s="16" t="s">
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="18">
-        <v>0</v>
-      </c>
-      <c r="E22" s="18">
-        <v>0</v>
-      </c>
-      <c r="F22" s="16" t="s">
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" outlineLevel="1">
-      <c r="B23" s="16" t="s">
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="18">
-        <v>0</v>
-      </c>
-      <c r="E23" s="18">
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
         <v>3.75</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.5" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="B24" s="14" t="s">
+    <row r="24" spans="1:7" ht="13.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="17">
-        <v>0</v>
-      </c>
-      <c r="E24" s="17">
+      <c r="D24" s="8">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
         <v>1.25</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:7" collapsed="1">
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="28" spans="1:7" ht="13.5" thickBot="1">
+    <row r="25" spans="1:7" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.5" thickBot="1">
-      <c r="B29" s="19" t="s">
+    <row r="29" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="16" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="10">
         <v>15</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="16" t="s">
+      <c r="G30" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="10">
         <v>-10</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.5" thickBot="1">
-      <c r="B32" s="14" t="s">
+    <row r="32" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="8">
         <v>5</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2284,161 +2373,517 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A49D6AD-508E-403E-933A-03EF1022438B}">
+  <sheetPr codeName="Hoja13"/>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="21"/>
+    </row>
+    <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="19">
+        <v>-31.25</v>
+      </c>
+      <c r="E16" s="19">
+        <v>-31.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="20">
+        <v>0.125</v>
+      </c>
+      <c r="E21" s="20">
+        <v>0.125</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="20">
+        <v>0</v>
+      </c>
+      <c r="E22" s="20">
+        <v>0</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="20">
+        <v>0</v>
+      </c>
+      <c r="E23" s="20">
+        <v>0</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="19">
+        <v>6.625</v>
+      </c>
+      <c r="E24" s="19">
+        <v>6.625</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="20">
+        <v>-6.5</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="18">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="20">
+        <v>-6</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="19">
+        <v>-7</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="16">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja14">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1"/>
+        <v>102</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
+      <c r="B2" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>6.625</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <f t="shared" ref="E4:E6" si="0">SUMPRODUCT($B$2:$D$2, B4:D4)</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="3">
+        <f>SUMPRODUCT($B$2:$E$2,B4:E4)</f>
+        <v>-6.5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4:H6" si="1">G4-E4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" ref="I4:I6" si="0">H4-F4</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
+      <c r="B5" s="3">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" ref="F5:F6" si="1">SUMPRODUCT($B$2:$E$2,B5:E5)</f>
+        <v>-6</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-6</v>
+      </c>
+      <c r="I5" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3">
+      <c r="B6" s="3">
+        <v>-3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>-10</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-7</v>
+      </c>
+      <c r="I6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="B7" s="3">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3">
+        <v>-20</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-5</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="2">
-        <f>SUMPRODUCT($B$2:$D$2, B7:D7)</f>
-        <v>0</v>
+        <f>SUMPRODUCT($B$2:$E$2,B7:E7)</f>
+        <v>-31.25</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FAB184-6C1B-49F8-B588-A22BFA1F04F8}">
+  <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -2449,71 +2894,71 @@
     <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:5" collapsed="1">
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:5" collapsed="1"/>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1">
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1">
+    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>70</v>
       </c>
@@ -2527,7 +2972,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1">
+    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
@@ -2541,12 +2986,12 @@
         <v>18.658536585365855</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.5" thickBot="1">
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.5" thickBot="1">
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>70</v>
       </c>
@@ -2563,7 +3008,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="13" t="s">
         <v>76</v>
       </c>
@@ -2572,7 +3017,7 @@
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
     </row>
-    <row r="22" spans="1:7" hidden="1" outlineLevel="1">
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="10" t="s">
         <v>48</v>
       </c>
@@ -2589,7 +3034,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" outlineLevel="1">
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="10" t="s">
         <v>51</v>
       </c>
@@ -2606,7 +3051,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.5" hidden="1" outlineLevel="1" thickBot="1">
+    <row r="24" spans="1:7" ht="13.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
         <v>53</v>
       </c>
@@ -2623,13 +3068,13 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:7" collapsed="1"/>
-    <row r="28" spans="1:7" ht="13.5" thickBot="1">
+    <row r="25" spans="1:7" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.5" thickBot="1">
+    <row r="29" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>70</v>
       </c>
@@ -2649,7 +3094,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B30" s="10" t="s">
         <v>73</v>
       </c>
@@ -2669,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B31" s="10" t="s">
         <v>74</v>
       </c>
@@ -2689,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.5" thickBot="1">
+    <row r="32" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="8" t="s">
         <v>75</v>
       </c>
@@ -2716,11 +3161,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="4" width="3" customWidth="1"/>
@@ -2730,7 +3175,7 @@
     <col min="8" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2748,7 +3193,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2766,7 +3211,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2786,7 +3231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -2812,7 +3257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2838,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2864,7 +3309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -2882,7 +3327,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -2905,8 +3350,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6849234-CA33-4D5D-8C80-785D4BA712FD}">
+  <sheetPr codeName="Hoja4"/>
   <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -2917,71 +3363,71 @@
     <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:5" collapsed="1">
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:5" collapsed="1"/>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1">
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1">
+    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>70</v>
       </c>
@@ -2995,7 +3441,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1">
+    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
@@ -3009,12 +3455,12 @@
         <v>18.658536585365855</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.5" thickBot="1">
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.5" thickBot="1">
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>70</v>
       </c>
@@ -3031,7 +3477,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="13" t="s">
         <v>76</v>
       </c>
@@ -3040,7 +3486,7 @@
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
     </row>
-    <row r="22" spans="1:7" hidden="1" outlineLevel="1">
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="10" t="s">
         <v>48</v>
       </c>
@@ -3057,7 +3503,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" outlineLevel="1">
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="10" t="s">
         <v>51</v>
       </c>
@@ -3074,7 +3520,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.5" hidden="1" outlineLevel="1" thickBot="1">
+    <row r="24" spans="1:7" ht="13.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
         <v>53</v>
       </c>
@@ -3091,13 +3537,13 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:7" collapsed="1"/>
-    <row r="28" spans="1:7" ht="13.5" thickBot="1">
+    <row r="25" spans="1:7" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.5" thickBot="1">
+    <row r="29" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>70</v>
       </c>
@@ -3117,7 +3563,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B30" s="10" t="s">
         <v>73</v>
       </c>
@@ -3137,7 +3583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B31" s="10" t="s">
         <v>74</v>
       </c>
@@ -3157,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.5" thickBot="1">
+    <row r="32" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="8" t="s">
         <v>75</v>
       </c>
@@ -3184,11 +3630,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja5">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:K32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="3" width="4.5703125" customWidth="1"/>
@@ -3200,7 +3646,7 @@
     <col min="9" max="9" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="12.75">
+    <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3221,7 +3667,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="12.75">
+    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3242,7 +3688,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" ht="12.75">
+    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3263,7 +3709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.75">
+    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -3294,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="12.75">
+    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -3325,7 +3771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="12.75">
+    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -3356,7 +3802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="12.75">
+    <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3377,7 +3823,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9" ht="12.75">
+    <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3393,10 +3839,10 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row r="21" spans="8:11" ht="15.75" customHeight="1">
+    <row r="21" spans="8:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H21" s="4"/>
     </row>
-    <row r="32" spans="8:11" ht="15.75" customHeight="1">
+    <row r="32" spans="8:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K32" s="4"/>
     </row>
   </sheetData>
@@ -3407,8 +3853,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE75D373-4E18-420E-8661-9424F10D1AD8}">
+  <sheetPr codeName="Hoja6"/>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -3419,70 +3866,70 @@
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1">
+    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1">
+    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>36</v>
       </c>
@@ -3496,7 +3943,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1">
+    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
@@ -3510,12 +3957,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.5" thickBot="1">
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.5" thickBot="1">
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>36</v>
       </c>
@@ -3532,7 +3979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="10" t="s">
         <v>48</v>
       </c>
@@ -3549,7 +3996,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
@@ -3566,7 +4013,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B23" s="10" t="s">
         <v>53</v>
       </c>
@@ -3583,7 +4030,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.5" thickBot="1">
+    <row r="24" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
         <v>55</v>
       </c>
@@ -3600,12 +4047,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="13.5" thickBot="1">
+    <row r="27" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="13.5" thickBot="1">
+    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>36</v>
       </c>
@@ -3625,7 +4072,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B29" s="10" t="s">
         <v>57</v>
       </c>
@@ -3645,7 +4092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B30" s="10" t="s">
         <v>61</v>
       </c>
@@ -3665,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="13.5" thickBot="1">
+    <row r="31" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>64</v>
       </c>
@@ -3692,11 +4139,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja7">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="4.140625" customWidth="1"/>
@@ -3711,7 +4158,7 @@
     <col min="11" max="11" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3738,7 +4185,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3765,7 +4212,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1">
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3788,7 +4235,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -3823,7 +4270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -3858,7 +4305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -3893,7 +4340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -3928,7 +4375,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -3955,7 +4402,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -3981,8 +4428,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B477F4A1-9004-447D-A946-6977D22B5582}">
+  <sheetPr codeName="Hoja8"/>
   <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -3993,327 +4441,327 @@
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.5" thickBot="1">
+    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" thickBot="1">
-      <c r="B15" s="15" t="s">
+    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" thickBot="1">
-      <c r="B16" s="14" t="s">
+    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="8">
         <v>15</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="8">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.5" thickBot="1">
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.5" thickBot="1">
-      <c r="B20" s="15" t="s">
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="B21" s="16" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="18">
-        <v>0</v>
-      </c>
-      <c r="E21" s="18">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16" t="s">
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="B22" s="16" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="10">
         <v>1</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="10">
         <v>1</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="B23" s="16" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="18">
-        <v>0</v>
-      </c>
-      <c r="E23" s="18">
-        <v>0</v>
-      </c>
-      <c r="F23" s="16" t="s">
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="16" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="18">
-        <v>0</v>
-      </c>
-      <c r="E24" s="18">
-        <v>0</v>
-      </c>
-      <c r="F24" s="16" t="s">
+      <c r="D24" s="10">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="16" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="18">
-        <v>0</v>
-      </c>
-      <c r="E25" s="18">
-        <v>0</v>
-      </c>
-      <c r="F25" s="16" t="s">
+      <c r="D25" s="10">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10">
+        <v>0</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="13.5" thickBot="1">
-      <c r="B26" s="14" t="s">
+    <row r="26" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D26" s="17">
-        <v>0</v>
-      </c>
-      <c r="E26" s="17">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14" t="s">
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.5" thickBot="1">
+    <row r="29" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="13.5" thickBot="1">
-      <c r="B30" s="15" t="s">
+    <row r="30" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="16" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="10">
         <v>1</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="B32" s="16" t="s">
+      <c r="G31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="10">
         <v>2</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G32" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
-      <c r="B33" s="16" t="s">
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B33" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="10">
         <v>3</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" ht="13.5" thickBot="1">
-      <c r="B34" s="14" t="s">
+      <c r="G33" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D34" s="17">
-        <v>0</v>
-      </c>
-      <c r="E34" s="14" t="s">
+      <c r="D34" s="8">
+        <v>0</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="M35" s="4"/>
     </row>
   </sheetData>
@@ -4323,11 +4771,11 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Hoja9">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="4" width="3" customWidth="1"/>
@@ -4337,7 +4785,7 @@
     <col min="8" max="8" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4355,7 +4803,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4367,7 +4815,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4387,7 +4835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -4405,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -4423,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -4441,7 +4889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -4459,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -4471,7 +4919,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>

--- a/Taller_Dualidad_Solver_Completo1.xlsx
+++ b/Taller_Dualidad_Solver_Completo1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66bf0d0917e3adb/Documentos/GitHub/ExcelSolverPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="971" documentId="8_{BA39E689-899D-490F-8B8B-B9FE1E44DD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8B954D-59FA-46B5-B5FD-81A0D7AF5D32}"/>
+  <xr:revisionPtr revIDLastSave="978" documentId="8_{BA39E689-899D-490F-8B8B-B9FE1E44DD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{851CD5BB-925F-43FA-94A8-BC59FFB796CC}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="11625" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E1 - Primal" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="E3 - Dual" sheetId="6" r:id="rId10"/>
     <sheet name="E4 - Primal" sheetId="7" r:id="rId11"/>
     <sheet name="Informe de respuestas 1" sheetId="17" r:id="rId12"/>
-    <sheet name="Answer Report 1" sheetId="22" r:id="rId13"/>
+    <sheet name="E4 - Informe Dual" sheetId="22" r:id="rId13"/>
     <sheet name="E4 - Dual" sheetId="8" r:id="rId14"/>
   </sheets>
   <definedNames>
@@ -252,7 +252,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="159">
   <si>
     <t>Variables</t>
   </si>
@@ -725,13 +725,10 @@
     <t>Tiempo de la solución: 0.078 segundos.</t>
   </si>
   <si>
-    <t>Iteraciones:: 2 Subproblemas: 0</t>
-  </si>
-  <si>
-    <t>Tiempo máximo Ilimitado,  Iteraciones: Unlimited, Precisión 0.000001, Usar escala automática</t>
-  </si>
-  <si>
     <t>Máximo de subproblemas Ilimitado, Máximo de soluciones de enteros Ilimitado, Tolerancia de enteros 1%, Asumir no negativo.</t>
+  </si>
+  <si>
+    <t>Tiempo máximo Ilimitado,  Iteraciones Ilimitado, Precisión 0.000001, Usar escala automática</t>
   </si>
 </sst>
 </file>
@@ -897,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,13 +921,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1333,6 +1323,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38968</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>48290</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4F1EDCA-77EA-C7BB-EFE5-C2977B921566}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="600075" y="1885950"/>
+          <a:ext cx="6220693" cy="4763165"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
@@ -2427,7 +2466,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -2442,11 +2481,11 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="M12" s="21"/>
+      <c r="M12" s="16"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -2454,30 +2493,30 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="8">
         <v>-31.25</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="8">
         <v>-31.25</v>
       </c>
     </row>
@@ -2487,87 +2526,87 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="10">
         <v>0.125</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="10">
         <v>0.125</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="20">
-        <v>0</v>
-      </c>
-      <c r="E22" s="20">
-        <v>0</v>
-      </c>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="20">
-        <v>0</v>
-      </c>
-      <c r="E23" s="20">
-        <v>0</v>
-      </c>
-      <c r="F23" s="18" t="s">
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="8">
         <v>6.625</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="8">
         <v>6.625</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2577,82 +2616,82 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G28" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="10">
         <v>-6.5</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="10">
         <v>11.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="10">
         <v>-6</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="8">
         <v>-7</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2861,10 +2900,7 @@
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2">
-        <f>SUMPRODUCT($B$2:$E$2,B7:E7)</f>
-        <v>-31.25</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2876,6 +2912,7 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Taller_Dualidad_Solver_Completo1.xlsx
+++ b/Taller_Dualidad_Solver_Completo1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66bf0d0917e3adb/Documentos/GitHub/ExcelSolverPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="978" documentId="8_{BA39E689-899D-490F-8B8B-B9FE1E44DD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{851CD5BB-925F-43FA-94A8-BC59FFB796CC}"/>
+  <xr:revisionPtr revIDLastSave="981" documentId="8_{BA39E689-899D-490F-8B8B-B9FE1E44DD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8380035-54F8-4314-89C5-80FC326F6237}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1333,10 +1333,10 @@
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>38968</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>48290</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200162</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1359,8 +1359,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="600075" y="1885950"/>
-          <a:ext cx="6220693" cy="4763165"/>
+          <a:off x="600075" y="1800225"/>
+          <a:ext cx="2933837" cy="2128837"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1160317</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>103910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>454211</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>121228</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94D41D14-3052-C761-208A-17A39A79FCF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4468090" y="1974274"/>
+          <a:ext cx="3225121" cy="2303318"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/Taller_Dualidad_Solver_Completo1.xlsx
+++ b/Taller_Dualidad_Solver_Completo1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66bf0d0917e3adb/Documentos/GitHub/ExcelSolverPL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leons\OneDrive\Desktop\Repos GIT\SolverExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="981" documentId="8_{BA39E689-899D-490F-8B8B-B9FE1E44DD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8380035-54F8-4314-89C5-80FC326F6237}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2D85B4-ED81-42AB-B51D-5DA8A08FCAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E1 - Primal" sheetId="1" r:id="rId1"/>
@@ -22,217 +22,249 @@
     <sheet name="E2 - Dual" sheetId="4" r:id="rId7"/>
     <sheet name="E2 - Informe Dual" sheetId="16" r:id="rId8"/>
     <sheet name="E3 - Primal" sheetId="5" r:id="rId9"/>
-    <sheet name="E3 - Dual" sheetId="6" r:id="rId10"/>
-    <sheet name="E4 - Primal" sheetId="7" r:id="rId11"/>
-    <sheet name="Informe de respuestas 1" sheetId="17" r:id="rId12"/>
-    <sheet name="E4 - Informe Dual" sheetId="22" r:id="rId13"/>
-    <sheet name="E4 - Dual" sheetId="8" r:id="rId14"/>
+    <sheet name="E3 - Informe Primal" sheetId="25" r:id="rId10"/>
+    <sheet name="E3 - Dual" sheetId="6" r:id="rId11"/>
+    <sheet name="E3 - Informe Dual" sheetId="26" r:id="rId12"/>
+    <sheet name="E4 - Primal" sheetId="7" r:id="rId13"/>
+    <sheet name="E4 - Informe Primal" sheetId="17" r:id="rId14"/>
+    <sheet name="E4 - Dual" sheetId="8" r:id="rId15"/>
+    <sheet name="E4 - Informe Dual" sheetId="22" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="2" hidden="1">'E1 - Dual'!$B$2:$D$2</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'E1 - Primal'!$B$2:$D$2</definedName>
     <definedName name="solver_adj" localSheetId="6" hidden="1">'E2 - Dual'!$B$2:$G$2</definedName>
     <definedName name="solver_adj" localSheetId="4" hidden="1">'E2 - Primal'!$B$2:$E$2</definedName>
-    <definedName name="solver_adj" localSheetId="13" hidden="1">'E4 - Dual'!$B$2:$E$2</definedName>
-    <definedName name="solver_adj" localSheetId="10" hidden="1">'E4 - Primal'!$B$2:$D$2</definedName>
+    <definedName name="solver_adj" localSheetId="8" hidden="1">'E3 - Primal'!$B$2:$D$2</definedName>
+    <definedName name="solver_adj" localSheetId="14" hidden="1">'E4 - Dual'!$B$2:$E$2</definedName>
+    <definedName name="solver_adj" localSheetId="12" hidden="1">'E4 - Primal'!$B$2:$D$2</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="13" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="10" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="8" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="14" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="12" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="12" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="13" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="12" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="12" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="13" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="12" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">'E1 - Dual'!$E$4</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'E1 - Primal'!$E$4</definedName>
     <definedName name="solver_lhs1" localSheetId="6" hidden="1">'E2 - Dual'!$H$4:$H$7</definedName>
     <definedName name="solver_lhs1" localSheetId="4" hidden="1">'E2 - Primal'!$F$4:$F$6</definedName>
-    <definedName name="solver_lhs1" localSheetId="13" hidden="1">'E4 - Dual'!$F$4:$F$6</definedName>
-    <definedName name="solver_lhs1" localSheetId="10" hidden="1">'E4 - Primal'!$E$4</definedName>
+    <definedName name="solver_lhs1" localSheetId="8" hidden="1">'E3 - Primal'!$E$4:$E$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="14" hidden="1">'E4 - Dual'!$F$4:$F$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="12" hidden="1">'E4 - Primal'!$E$4</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'E1 - Dual'!$E$5</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'E1 - Primal'!$E$5</definedName>
     <definedName name="solver_lhs2" localSheetId="4" hidden="1">'E2 - Primal'!$B$6:$E$6</definedName>
-    <definedName name="solver_lhs2" localSheetId="10" hidden="1">'E4 - Primal'!$E$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="12" hidden="1">'E4 - Primal'!$E$5</definedName>
     <definedName name="solver_lhs3" localSheetId="2" hidden="1">'E1 - Dual'!$E$6</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">'E1 - Primal'!$E$6</definedName>
     <definedName name="solver_lhs3" localSheetId="4" hidden="1">'E2 - Primal'!$B$6:$E$6</definedName>
-    <definedName name="solver_lhs3" localSheetId="10" hidden="1">'E4 - Primal'!$E$6</definedName>
+    <definedName name="solver_lhs3" localSheetId="12" hidden="1">'E4 - Primal'!$E$6</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="13" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="12" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="13" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="10" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="8" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="14" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="12" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="13" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="10" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="8" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="14" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="12" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="13" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="12" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="12" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="13" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="12" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="12" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="12" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">'E1 - Dual'!$B$8</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'E1 - Primal'!$B$8</definedName>
     <definedName name="solver_opt" localSheetId="6" hidden="1">'E2 - Dual'!$B$9</definedName>
     <definedName name="solver_opt" localSheetId="4" hidden="1">'E2 - Primal'!$B$8</definedName>
-    <definedName name="solver_opt" localSheetId="13" hidden="1">'E4 - Dual'!$B$8</definedName>
-    <definedName name="solver_opt" localSheetId="10" hidden="1">'E4 - Primal'!$B$8</definedName>
+    <definedName name="solver_opt" localSheetId="8" hidden="1">'E3 - Primal'!$B$9</definedName>
+    <definedName name="solver_opt" localSheetId="14" hidden="1">'E4 - Dual'!$B$8</definedName>
+    <definedName name="solver_opt" localSheetId="12" hidden="1">'E4 - Primal'!$B$8</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="13" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="10" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="8" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="14" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="12" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="12" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_rel1" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="12" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_rel2" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="12" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_rel3" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="12" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">'E1 - Dual'!$G$4</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'E1 - Primal'!$G$4</definedName>
     <definedName name="solver_rhs1" localSheetId="6" hidden="1">'E2 - Dual'!$J$4:$J$7</definedName>
     <definedName name="solver_rhs1" localSheetId="4" hidden="1">'E2 - Primal'!$H$4:$H$6</definedName>
-    <definedName name="solver_rhs1" localSheetId="13" hidden="1">'E4 - Dual'!$H$4:$H$6</definedName>
-    <definedName name="solver_rhs1" localSheetId="10" hidden="1">'E4 - Primal'!$G$4</definedName>
+    <definedName name="solver_rhs1" localSheetId="8" hidden="1">'E3 - Primal'!$G$4:$G$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="14" hidden="1">'E4 - Dual'!$H$4:$H$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="12" hidden="1">'E4 - Primal'!$G$4</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">'E1 - Dual'!$G$5</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'E1 - Primal'!$G$5</definedName>
     <definedName name="solver_rhs2" localSheetId="4" hidden="1">'E2 - Primal'!$H$6</definedName>
-    <definedName name="solver_rhs2" localSheetId="10" hidden="1">'E4 - Primal'!$G$5</definedName>
+    <definedName name="solver_rhs2" localSheetId="12" hidden="1">'E4 - Primal'!$G$5</definedName>
     <definedName name="solver_rhs3" localSheetId="2" hidden="1">'E1 - Dual'!$G$6</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">'E1 - Primal'!$G$6</definedName>
     <definedName name="solver_rhs3" localSheetId="4" hidden="1">'E2 - Primal'!$H$6</definedName>
-    <definedName name="solver_rhs3" localSheetId="10" hidden="1">'E4 - Primal'!$G$6</definedName>
+    <definedName name="solver_rhs3" localSheetId="12" hidden="1">'E4 - Primal'!$G$6</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="13" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="12" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="13" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="14" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="12" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="12" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="13" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="12" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="13" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="10" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="8" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="14" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="12" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="13" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="12" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="4" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="13" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="10" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="8" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="14" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="12" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="13" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="12" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="13" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="14" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="12" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="13" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="14" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="12" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -243,8 +275,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -252,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="170">
   <si>
     <t>Variables</t>
   </si>
@@ -729,6 +759,39 @@
   </si>
   <si>
     <t>Tiempo máximo Ilimitado,  Iteraciones Ilimitado, Precisión 0.000001, Usar escala automática</t>
+  </si>
+  <si>
+    <t>$E$7</t>
+  </si>
+  <si>
+    <t>$E$4=$G$4</t>
+  </si>
+  <si>
+    <t>$E$7&gt;=$G$7</t>
+  </si>
+  <si>
+    <t>Hoja de cálculo: [Taller_Dualidad_Solver_Completo.xlsx]E3 - Primal</t>
+  </si>
+  <si>
+    <t>Informe creado: 24/10/2026 6:39:30 p. m.</t>
+  </si>
+  <si>
+    <t>Tiempo de la solución: 0,031 segundos.</t>
+  </si>
+  <si>
+    <t>Hoja de cálculo: [Taller_Dualidad_Solver_Completo.xlsx]E3 - Dual</t>
+  </si>
+  <si>
+    <t>Informe creado: 24/10/2026 6:51:40 p. m.</t>
+  </si>
+  <si>
+    <t>$F$4&gt;=$H$4</t>
+  </si>
+  <si>
+    <t>$F$5&gt;=$H$5</t>
+  </si>
+  <si>
+    <t>$F$6&gt;=$H$6</t>
   </si>
 </sst>
 </file>
@@ -1279,6 +1342,116 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>619379</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74D69386-574F-0925-D7CE-1B71978D4128}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5600700" y="0"/>
+          <a:ext cx="4629404" cy="4952999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>240765</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCC7C8A4-4754-BAD7-F13D-3048EFCE52F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6076950" y="66675"/>
+          <a:ext cx="3288765" cy="3838575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>712488</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>133349</xdr:rowOff>
@@ -1323,7 +1496,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1819,15 +1992,298 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC3A13B-1A18-4EBB-BCC6-B2570B606292}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <v>6850</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>150</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <v>850</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="10">
+        <v>1000</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="10">
+        <v>150</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="8">
+        <v>850</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" s="8">
+        <v>650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Hoja10">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="5" width="3" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" customWidth="1"/>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
@@ -1859,10 +2315,18 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="2">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1893,35 +2357,59 @@
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
       <c r="F4" s="3">
         <f t="shared" ref="F4:F6" si="0">SUMPRODUCT($B$2:$E$2, B4:E4)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" s="3">
+        <v>5</v>
+      </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4:I6" si="1">H4-F4</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="3">
+        <v>6</v>
+      </c>
       <c r="I5" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1931,16 +2419,28 @@
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>-1</v>
+      </c>
       <c r="F6" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="3">
+        <v>7</v>
+      </c>
       <c r="I6" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1950,10 +2450,18 @@
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="B7" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>300</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-150</v>
+      </c>
+      <c r="E7" s="3">
+        <v>-200</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -1965,7 +2473,7 @@
       </c>
       <c r="B8" s="2">
         <f>SUMPRODUCT($B$2:$E$2, B7:E7)</f>
-        <v>0</v>
+        <v>6850</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -1975,12 +2483,292 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
+    <row r="24" spans="15:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O24" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B62F08-430E-416B-86FB-15EE360D908A}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <v>6850</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
+        <v>7</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="10">
+        <v>7</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="10">
+        <v>6</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="8">
+        <v>7</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja11">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2176,7 +2964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C1062C-39FD-49D7-AF33-C56F9F03DC1B}">
   <sheetPr codeName="Hoja12"/>
   <dimension ref="A1:G32"/>
@@ -2455,296 +3243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A49D6AD-508E-403E-933A-03EF1022438B}">
-  <sheetPr codeName="Hoja13"/>
-  <dimension ref="A1:M31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="2.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="M12" s="16"/>
-    </row>
-    <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="8">
-        <v>-31.25</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-31.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="10">
-        <v>0.125</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0.125</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="10">
-        <v>0</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" s="10">
-        <v>0</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" s="8">
-        <v>6.625</v>
-      </c>
-      <c r="E24" s="8">
-        <v>6.625</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="10">
-        <v>-6.5</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="G29" s="10">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B30" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="10">
-        <v>-6</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="8">
-        <v>-7</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" s="8">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Hoja14">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2957,6 +3456,295 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A49D6AD-508E-403E-933A-03EF1022438B}">
+  <sheetPr codeName="Hoja13"/>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="16"/>
+    </row>
+    <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-31.25</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-31.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="8">
+        <v>6.625</v>
+      </c>
+      <c r="E24" s="8">
+        <v>6.625</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="10">
+        <v>-6.5</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="10">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="10">
+        <v>-6</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="8">
+        <v>-7</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4859,7 +5647,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="4" width="3" customWidth="1"/>
+    <col min="2" max="2" width="5" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" customWidth="1"/>
@@ -4888,9 +5678,15 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>150</v>
+      </c>
+      <c r="D2" s="2">
+        <v>850</v>
+      </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -4920,15 +5716,25 @@
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
       <c r="E4" s="3">
-        <f t="shared" ref="E4:E7" si="0">SUMPRODUCT($B$2:$D$2, B4:D4)</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+        <f t="shared" ref="E4:E6" si="0">SUMPRODUCT($B$2:$D$2, B4:D4)</f>
+        <v>1000</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1000</v>
+      </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H7" si="1">G4-E4</f>
         <v>0</v>
@@ -4938,33 +5744,53 @@
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="3">
+        <v>300</v>
+      </c>
       <c r="H5" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
       <c r="E6" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="3">
+        <v>150</v>
+      </c>
       <c r="H6" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4974,28 +5800,47 @@
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
       <c r="E7" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+        <f>SUMPRODUCT($B$2:$D$2, B7:D7)</f>
+        <v>850</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="3">
+        <v>200</v>
+      </c>
       <c r="H7" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
+        <f>SUMPRODUCT($B$2:$D$2, B8:D8)</f>
+        <v>6850</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -5006,7 +5851,7 @@
       </c>
       <c r="B9" s="2">
         <f>SUMPRODUCT($B$2:$D$2, B8:D8)</f>
-        <v>0</v>
+        <v>6850</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -5017,5 +5862,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Taller_Dualidad_Solver_Completo1.xlsx
+++ b/Taller_Dualidad_Solver_Completo1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leons\OneDrive\Desktop\Repos GIT\SolverExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2D85B4-ED81-42AB-B51D-5DA8A08FCAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90194F9B-D240-488F-A11D-0F9D5CC889A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E1 - Primal" sheetId="1" r:id="rId1"/>
@@ -3443,7 +3443,9 @@
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>-31.25</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
